--- a/Backend/income_details.xlsx
+++ b/Backend/income_details.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,21 +415,63 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Work</v>
+      </c>
+      <c r="B2">
+        <v>1200</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="D2" t="str">
+        <v>5/12/2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Freelance Project</v>
+      </c>
+      <c r="B3">
+        <v>1200</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="D3" t="str">
+        <v>5/12/2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Freelance Earning</v>
+      </c>
+      <c r="B4">
+        <v>10000</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Freelance</v>
+      </c>
+      <c r="D4" t="str">
+        <v>5/11/2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>Web Project</v>
       </c>
-      <c r="B2">
+      <c r="B5">
         <v>15000</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C5" t="str">
         <v>freelancing</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D5" t="str">
         <v>4/9/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>